--- a/docs/test-plans/qapulse-smoke-tests.xlsx
+++ b/docs/test-plans/qapulse-smoke-tests.xlsx
@@ -1844,7 +1844,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="en-US"/>
               </a:p>
@@ -2190,7 +2190,7 @@
                 </a:defRPr>
               </a:pPr>
               <a:r>
-                <a:t/>
+                <a:t>None</a:t>
               </a:r>
               <a:endParaRPr lang="en-US"/>
             </a:p>
@@ -2267,7 +2267,7 @@
                 </a:defRPr>
               </a:pPr>
               <a:r>
-                <a:t/>
+                <a:t>None</a:t>
               </a:r>
               <a:endParaRPr lang="en-US"/>
             </a:p>
@@ -2300,7 +2300,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="en-US"/>
           </a:p>
@@ -2404,7 +2404,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="en-US"/>
           </a:p>
@@ -2458,7 +2458,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="en-US"/>
         </a:p>
@@ -4075,7 +4075,11 @@
       </c>
       <c r="J2" s="177" t="inlineStr"/>
       <c r="K2" s="177" t="inlineStr"/>
-      <c r="L2" s="177" t="inlineStr"/>
+      <c r="L2" s="177" t="inlineStr">
+        <is>
+          <t>Automated — artifacts/qa-automation/tests/smoke.spec.ts:15</t>
+        </is>
+      </c>
       <c r="M2" s="177" t="inlineStr"/>
     </row>
     <row r="3">
@@ -4124,7 +4128,11 @@
       </c>
       <c r="J3" s="177" t="inlineStr"/>
       <c r="K3" s="177" t="inlineStr"/>
-      <c r="L3" s="177" t="inlineStr"/>
+      <c r="L3" s="177" t="inlineStr">
+        <is>
+          <t>Automated — artifacts/qa-automation/tests/smoke.spec.ts:20</t>
+        </is>
+      </c>
       <c r="M3" s="177" t="inlineStr"/>
     </row>
     <row r="4">
@@ -4172,7 +4180,11 @@
       </c>
       <c r="J4" s="177" t="inlineStr"/>
       <c r="K4" s="177" t="inlineStr"/>
-      <c r="L4" s="177" t="inlineStr"/>
+      <c r="L4" s="177" t="inlineStr">
+        <is>
+          <t>Automated — artifacts/qa-automation/tests/smoke.spec.ts:26</t>
+        </is>
+      </c>
       <c r="M4" s="177" t="inlineStr"/>
     </row>
     <row r="5">
@@ -4220,7 +4232,11 @@
       </c>
       <c r="J5" s="177" t="inlineStr"/>
       <c r="K5" s="177" t="inlineStr"/>
-      <c r="L5" s="177" t="inlineStr"/>
+      <c r="L5" s="177" t="inlineStr">
+        <is>
+          <t>Automated — artifacts/qa-automation/tests/smoke.spec.ts:40</t>
+        </is>
+      </c>
       <c r="M5" s="177" t="inlineStr"/>
     </row>
     <row r="6">
@@ -4268,7 +4284,11 @@
       </c>
       <c r="J6" s="177" t="inlineStr"/>
       <c r="K6" s="177" t="inlineStr"/>
-      <c r="L6" s="177" t="inlineStr"/>
+      <c r="L6" s="177" t="inlineStr">
+        <is>
+          <t>Automated — artifacts/qa-automation/tests/smoke.spec.ts:46</t>
+        </is>
+      </c>
       <c r="M6" s="177" t="inlineStr"/>
     </row>
     <row r="7">
@@ -4316,7 +4336,11 @@
       </c>
       <c r="J7" s="177" t="inlineStr"/>
       <c r="K7" s="177" t="inlineStr"/>
-      <c r="L7" s="177" t="inlineStr"/>
+      <c r="L7" s="177" t="inlineStr">
+        <is>
+          <t>Automated — artifacts/qa-automation/tests/smoke.spec.ts:56</t>
+        </is>
+      </c>
       <c r="M7" s="177" t="inlineStr"/>
     </row>
     <row r="8">
@@ -4363,7 +4387,11 @@
       </c>
       <c r="J8" s="177" t="inlineStr"/>
       <c r="K8" s="177" t="inlineStr"/>
-      <c r="L8" s="177" t="inlineStr"/>
+      <c r="L8" s="177" t="inlineStr">
+        <is>
+          <t>Automated — artifacts/qa-automation/tests/smoke.spec.ts:67</t>
+        </is>
+      </c>
       <c r="M8" s="177" t="inlineStr"/>
     </row>
     <row r="9">
@@ -4412,7 +4440,11 @@
       </c>
       <c r="J9" s="177" t="inlineStr"/>
       <c r="K9" s="177" t="inlineStr"/>
-      <c r="L9" s="177" t="inlineStr"/>
+      <c r="L9" s="177" t="inlineStr">
+        <is>
+          <t>Automated — artifacts/qa-automation/tests/smoke.spec.ts:76</t>
+        </is>
+      </c>
       <c r="M9" s="177" t="inlineStr"/>
     </row>
     <row r="10">
@@ -4460,7 +4492,11 @@
       </c>
       <c r="J10" s="177" t="inlineStr"/>
       <c r="K10" s="177" t="inlineStr"/>
-      <c r="L10" s="177" t="inlineStr"/>
+      <c r="L10" s="177" t="inlineStr">
+        <is>
+          <t>Automated — artifacts/qa-automation/tests/smoke.spec.ts:85</t>
+        </is>
+      </c>
       <c r="M10" s="177" t="inlineStr"/>
     </row>
     <row r="11">
@@ -4508,7 +4544,11 @@
       </c>
       <c r="J11" s="177" t="inlineStr"/>
       <c r="K11" s="177" t="inlineStr"/>
-      <c r="L11" s="177" t="inlineStr"/>
+      <c r="L11" s="177" t="inlineStr">
+        <is>
+          <t>Automated — artifacts/qa-automation/tests/smoke.spec.ts:96</t>
+        </is>
+      </c>
       <c r="M11" s="177" t="inlineStr"/>
     </row>
     <row r="12">
@@ -4556,7 +4596,11 @@
       </c>
       <c r="J12" s="177" t="inlineStr"/>
       <c r="K12" s="177" t="inlineStr"/>
-      <c r="L12" s="177" t="inlineStr"/>
+      <c r="L12" s="177" t="inlineStr">
+        <is>
+          <t>Automated — artifacts/qa-automation/tests/smoke.spec.ts:106</t>
+        </is>
+      </c>
       <c r="M12" s="177" t="inlineStr"/>
     </row>
     <row r="13">
@@ -4604,7 +4648,11 @@
       </c>
       <c r="J13" s="177" t="inlineStr"/>
       <c r="K13" s="177" t="inlineStr"/>
-      <c r="L13" s="177" t="inlineStr"/>
+      <c r="L13" s="177" t="inlineStr">
+        <is>
+          <t>Automated — artifacts/qa-automation/tests/smoke.spec.ts:123</t>
+        </is>
+      </c>
       <c r="M13" s="177" t="inlineStr"/>
     </row>
     <row r="14">
@@ -4652,7 +4700,11 @@
       </c>
       <c r="J14" s="177" t="inlineStr"/>
       <c r="K14" s="177" t="inlineStr"/>
-      <c r="L14" s="177" t="inlineStr"/>
+      <c r="L14" s="177" t="inlineStr">
+        <is>
+          <t>Automated — artifacts/qa-automation/tests/smoke.spec.ts:136</t>
+        </is>
+      </c>
       <c r="M14" s="177" t="inlineStr"/>
     </row>
     <row r="15">
@@ -4700,7 +4752,11 @@
       </c>
       <c r="J15" s="177" t="inlineStr"/>
       <c r="K15" s="177" t="inlineStr"/>
-      <c r="L15" s="177" t="inlineStr"/>
+      <c r="L15" s="177" t="inlineStr">
+        <is>
+          <t>Automated — artifacts/qa-automation/tests/smoke.spec.ts:146</t>
+        </is>
+      </c>
       <c r="M15" s="177" t="inlineStr"/>
     </row>
     <row r="16">
@@ -4748,7 +4804,11 @@
       </c>
       <c r="J16" s="177" t="inlineStr"/>
       <c r="K16" s="177" t="inlineStr"/>
-      <c r="L16" s="177" t="inlineStr"/>
+      <c r="L16" s="177" t="inlineStr">
+        <is>
+          <t>Automated — artifacts/qa-automation/tests/smoke.spec.ts:160</t>
+        </is>
+      </c>
       <c r="M16" s="177" t="inlineStr"/>
     </row>
     <row r="17">
@@ -4796,7 +4856,11 @@
       </c>
       <c r="J17" s="177" t="inlineStr"/>
       <c r="K17" s="177" t="inlineStr"/>
-      <c r="L17" s="177" t="inlineStr"/>
+      <c r="L17" s="177" t="inlineStr">
+        <is>
+          <t>Automated — artifacts/qa-automation/tests/smoke.spec.ts:174</t>
+        </is>
+      </c>
       <c r="M17" s="177" t="inlineStr"/>
     </row>
     <row r="18">
@@ -4844,7 +4908,11 @@
       </c>
       <c r="J18" s="177" t="inlineStr"/>
       <c r="K18" s="177" t="inlineStr"/>
-      <c r="L18" s="177" t="inlineStr"/>
+      <c r="L18" s="177" t="inlineStr">
+        <is>
+          <t>Automated — artifacts/qa-automation/tests/smoke.spec.ts:196</t>
+        </is>
+      </c>
       <c r="M18" s="177" t="inlineStr"/>
     </row>
     <row r="19">
@@ -4893,7 +4961,11 @@
       </c>
       <c r="J19" s="177" t="inlineStr"/>
       <c r="K19" s="177" t="inlineStr"/>
-      <c r="L19" s="177" t="inlineStr"/>
+      <c r="L19" s="177" t="inlineStr">
+        <is>
+          <t>Automated — artifacts/qa-automation/tests/smoke.spec.ts:207</t>
+        </is>
+      </c>
       <c r="M19" s="177" t="inlineStr"/>
     </row>
     <row r="20">
@@ -4941,7 +5013,11 @@
       </c>
       <c r="J20" s="177" t="inlineStr"/>
       <c r="K20" s="177" t="inlineStr"/>
-      <c r="L20" s="177" t="inlineStr"/>
+      <c r="L20" s="177" t="inlineStr">
+        <is>
+          <t>Automated — artifacts/qa-automation/tests/smoke.spec.ts:241</t>
+        </is>
+      </c>
       <c r="M20" s="177" t="inlineStr"/>
     </row>
     <row r="21">
@@ -4988,7 +5064,11 @@
       </c>
       <c r="J21" s="177" t="inlineStr"/>
       <c r="K21" s="177" t="inlineStr"/>
-      <c r="L21" s="177" t="inlineStr"/>
+      <c r="L21" s="177" t="inlineStr">
+        <is>
+          <t>Automated — artifacts/qa-automation/tests/smoke.spec.ts:259</t>
+        </is>
+      </c>
       <c r="M21" s="177" t="inlineStr"/>
     </row>
     <row r="22">
@@ -5036,7 +5116,11 @@
       </c>
       <c r="J22" s="177" t="inlineStr"/>
       <c r="K22" s="177" t="inlineStr"/>
-      <c r="L22" s="177" t="inlineStr"/>
+      <c r="L22" s="177" t="inlineStr">
+        <is>
+          <t>Automated — artifacts/qa-automation/tests/smoke.spec.ts:289</t>
+        </is>
+      </c>
       <c r="M22" s="177" t="inlineStr"/>
     </row>
     <row r="23">
@@ -5084,7 +5168,11 @@
       </c>
       <c r="J23" s="177" t="inlineStr"/>
       <c r="K23" s="177" t="inlineStr"/>
-      <c r="L23" s="177" t="inlineStr"/>
+      <c r="L23" s="177" t="inlineStr">
+        <is>
+          <t>Automated — artifacts/qa-automation/tests/smoke.spec.ts:295</t>
+        </is>
+      </c>
       <c r="M23" s="177" t="inlineStr"/>
     </row>
     <row r="24">
@@ -5132,7 +5220,11 @@
       </c>
       <c r="J24" s="177" t="inlineStr"/>
       <c r="K24" s="177" t="inlineStr"/>
-      <c r="L24" s="177" t="inlineStr"/>
+      <c r="L24" s="177" t="inlineStr">
+        <is>
+          <t>Automated — artifacts/qa-automation/tests/smoke.spec.ts:303</t>
+        </is>
+      </c>
       <c r="M24" s="177" t="inlineStr"/>
     </row>
   </sheetData>

--- a/docs/test-plans/qapulse-smoke-tests.xlsx
+++ b/docs/test-plans/qapulse-smoke-tests.xlsx
@@ -1844,7 +1844,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t>None</a:t>
+                  <a:t/>
                 </a:r>
                 <a:endParaRPr lang="en-US"/>
               </a:p>
@@ -2190,7 +2190,7 @@
                 </a:defRPr>
               </a:pPr>
               <a:r>
-                <a:t>None</a:t>
+                <a:t/>
               </a:r>
               <a:endParaRPr lang="en-US"/>
             </a:p>
@@ -2267,7 +2267,7 @@
                 </a:defRPr>
               </a:pPr>
               <a:r>
-                <a:t>None</a:t>
+                <a:t/>
               </a:r>
               <a:endParaRPr lang="en-US"/>
             </a:p>
@@ -2300,7 +2300,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t>None</a:t>
+              <a:t/>
             </a:r>
             <a:endParaRPr lang="en-US"/>
           </a:p>
@@ -2404,7 +2404,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t>None</a:t>
+              <a:t/>
             </a:r>
             <a:endParaRPr lang="en-US"/>
           </a:p>
@@ -2458,7 +2458,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t>None</a:t>
+            <a:t/>
           </a:r>
           <a:endParaRPr lang="en-US"/>
         </a:p>
@@ -4075,11 +4075,7 @@
       </c>
       <c r="J2" s="177" t="inlineStr"/>
       <c r="K2" s="177" t="inlineStr"/>
-      <c r="L2" s="177" t="inlineStr">
-        <is>
-          <t>Automated — artifacts/qa-automation/tests/smoke.spec.ts:15</t>
-        </is>
-      </c>
+      <c r="L2" s="177" t="inlineStr"/>
       <c r="M2" s="177" t="inlineStr"/>
     </row>
     <row r="3">
@@ -4128,11 +4124,7 @@
       </c>
       <c r="J3" s="177" t="inlineStr"/>
       <c r="K3" s="177" t="inlineStr"/>
-      <c r="L3" s="177" t="inlineStr">
-        <is>
-          <t>Automated — artifacts/qa-automation/tests/smoke.spec.ts:20</t>
-        </is>
-      </c>
+      <c r="L3" s="177" t="inlineStr"/>
       <c r="M3" s="177" t="inlineStr"/>
     </row>
     <row r="4">
@@ -4180,11 +4172,7 @@
       </c>
       <c r="J4" s="177" t="inlineStr"/>
       <c r="K4" s="177" t="inlineStr"/>
-      <c r="L4" s="177" t="inlineStr">
-        <is>
-          <t>Automated — artifacts/qa-automation/tests/smoke.spec.ts:26</t>
-        </is>
-      </c>
+      <c r="L4" s="177" t="inlineStr"/>
       <c r="M4" s="177" t="inlineStr"/>
     </row>
     <row r="5">
@@ -4232,11 +4220,7 @@
       </c>
       <c r="J5" s="177" t="inlineStr"/>
       <c r="K5" s="177" t="inlineStr"/>
-      <c r="L5" s="177" t="inlineStr">
-        <is>
-          <t>Automated — artifacts/qa-automation/tests/smoke.spec.ts:40</t>
-        </is>
-      </c>
+      <c r="L5" s="177" t="inlineStr"/>
       <c r="M5" s="177" t="inlineStr"/>
     </row>
     <row r="6">
@@ -4284,11 +4268,7 @@
       </c>
       <c r="J6" s="177" t="inlineStr"/>
       <c r="K6" s="177" t="inlineStr"/>
-      <c r="L6" s="177" t="inlineStr">
-        <is>
-          <t>Automated — artifacts/qa-automation/tests/smoke.spec.ts:46</t>
-        </is>
-      </c>
+      <c r="L6" s="177" t="inlineStr"/>
       <c r="M6" s="177" t="inlineStr"/>
     </row>
     <row r="7">
@@ -4336,11 +4316,7 @@
       </c>
       <c r="J7" s="177" t="inlineStr"/>
       <c r="K7" s="177" t="inlineStr"/>
-      <c r="L7" s="177" t="inlineStr">
-        <is>
-          <t>Automated — artifacts/qa-automation/tests/smoke.spec.ts:56</t>
-        </is>
-      </c>
+      <c r="L7" s="177" t="inlineStr"/>
       <c r="M7" s="177" t="inlineStr"/>
     </row>
     <row r="8">
@@ -4387,11 +4363,7 @@
       </c>
       <c r="J8" s="177" t="inlineStr"/>
       <c r="K8" s="177" t="inlineStr"/>
-      <c r="L8" s="177" t="inlineStr">
-        <is>
-          <t>Automated — artifacts/qa-automation/tests/smoke.spec.ts:67</t>
-        </is>
-      </c>
+      <c r="L8" s="177" t="inlineStr"/>
       <c r="M8" s="177" t="inlineStr"/>
     </row>
     <row r="9">
@@ -4440,11 +4412,7 @@
       </c>
       <c r="J9" s="177" t="inlineStr"/>
       <c r="K9" s="177" t="inlineStr"/>
-      <c r="L9" s="177" t="inlineStr">
-        <is>
-          <t>Automated — artifacts/qa-automation/tests/smoke.spec.ts:76</t>
-        </is>
-      </c>
+      <c r="L9" s="177" t="inlineStr"/>
       <c r="M9" s="177" t="inlineStr"/>
     </row>
     <row r="10">
@@ -4492,11 +4460,7 @@
       </c>
       <c r="J10" s="177" t="inlineStr"/>
       <c r="K10" s="177" t="inlineStr"/>
-      <c r="L10" s="177" t="inlineStr">
-        <is>
-          <t>Automated — artifacts/qa-automation/tests/smoke.spec.ts:85</t>
-        </is>
-      </c>
+      <c r="L10" s="177" t="inlineStr"/>
       <c r="M10" s="177" t="inlineStr"/>
     </row>
     <row r="11">
@@ -4544,11 +4508,7 @@
       </c>
       <c r="J11" s="177" t="inlineStr"/>
       <c r="K11" s="177" t="inlineStr"/>
-      <c r="L11" s="177" t="inlineStr">
-        <is>
-          <t>Automated — artifacts/qa-automation/tests/smoke.spec.ts:96</t>
-        </is>
-      </c>
+      <c r="L11" s="177" t="inlineStr"/>
       <c r="M11" s="177" t="inlineStr"/>
     </row>
     <row r="12">
@@ -4596,11 +4556,7 @@
       </c>
       <c r="J12" s="177" t="inlineStr"/>
       <c r="K12" s="177" t="inlineStr"/>
-      <c r="L12" s="177" t="inlineStr">
-        <is>
-          <t>Automated — artifacts/qa-automation/tests/smoke.spec.ts:106</t>
-        </is>
-      </c>
+      <c r="L12" s="177" t="inlineStr"/>
       <c r="M12" s="177" t="inlineStr"/>
     </row>
     <row r="13">
@@ -4648,11 +4604,7 @@
       </c>
       <c r="J13" s="177" t="inlineStr"/>
       <c r="K13" s="177" t="inlineStr"/>
-      <c r="L13" s="177" t="inlineStr">
-        <is>
-          <t>Automated — artifacts/qa-automation/tests/smoke.spec.ts:123</t>
-        </is>
-      </c>
+      <c r="L13" s="177" t="inlineStr"/>
       <c r="M13" s="177" t="inlineStr"/>
     </row>
     <row r="14">
@@ -4700,11 +4652,7 @@
       </c>
       <c r="J14" s="177" t="inlineStr"/>
       <c r="K14" s="177" t="inlineStr"/>
-      <c r="L14" s="177" t="inlineStr">
-        <is>
-          <t>Automated — artifacts/qa-automation/tests/smoke.spec.ts:136</t>
-        </is>
-      </c>
+      <c r="L14" s="177" t="inlineStr"/>
       <c r="M14" s="177" t="inlineStr"/>
     </row>
     <row r="15">
@@ -4752,11 +4700,7 @@
       </c>
       <c r="J15" s="177" t="inlineStr"/>
       <c r="K15" s="177" t="inlineStr"/>
-      <c r="L15" s="177" t="inlineStr">
-        <is>
-          <t>Automated — artifacts/qa-automation/tests/smoke.spec.ts:146</t>
-        </is>
-      </c>
+      <c r="L15" s="177" t="inlineStr"/>
       <c r="M15" s="177" t="inlineStr"/>
     </row>
     <row r="16">
@@ -4804,11 +4748,7 @@
       </c>
       <c r="J16" s="177" t="inlineStr"/>
       <c r="K16" s="177" t="inlineStr"/>
-      <c r="L16" s="177" t="inlineStr">
-        <is>
-          <t>Automated — artifacts/qa-automation/tests/smoke.spec.ts:160</t>
-        </is>
-      </c>
+      <c r="L16" s="177" t="inlineStr"/>
       <c r="M16" s="177" t="inlineStr"/>
     </row>
     <row r="17">
@@ -4856,11 +4796,7 @@
       </c>
       <c r="J17" s="177" t="inlineStr"/>
       <c r="K17" s="177" t="inlineStr"/>
-      <c r="L17" s="177" t="inlineStr">
-        <is>
-          <t>Automated — artifacts/qa-automation/tests/smoke.spec.ts:174</t>
-        </is>
-      </c>
+      <c r="L17" s="177" t="inlineStr"/>
       <c r="M17" s="177" t="inlineStr"/>
     </row>
     <row r="18">
@@ -4908,11 +4844,7 @@
       </c>
       <c r="J18" s="177" t="inlineStr"/>
       <c r="K18" s="177" t="inlineStr"/>
-      <c r="L18" s="177" t="inlineStr">
-        <is>
-          <t>Automated — artifacts/qa-automation/tests/smoke.spec.ts:196</t>
-        </is>
-      </c>
+      <c r="L18" s="177" t="inlineStr"/>
       <c r="M18" s="177" t="inlineStr"/>
     </row>
     <row r="19">
@@ -4961,11 +4893,7 @@
       </c>
       <c r="J19" s="177" t="inlineStr"/>
       <c r="K19" s="177" t="inlineStr"/>
-      <c r="L19" s="177" t="inlineStr">
-        <is>
-          <t>Automated — artifacts/qa-automation/tests/smoke.spec.ts:207</t>
-        </is>
-      </c>
+      <c r="L19" s="177" t="inlineStr"/>
       <c r="M19" s="177" t="inlineStr"/>
     </row>
     <row r="20">
@@ -5013,11 +4941,7 @@
       </c>
       <c r="J20" s="177" t="inlineStr"/>
       <c r="K20" s="177" t="inlineStr"/>
-      <c r="L20" s="177" t="inlineStr">
-        <is>
-          <t>Automated — artifacts/qa-automation/tests/smoke.spec.ts:241</t>
-        </is>
-      </c>
+      <c r="L20" s="177" t="inlineStr"/>
       <c r="M20" s="177" t="inlineStr"/>
     </row>
     <row r="21">
@@ -5064,11 +4988,7 @@
       </c>
       <c r="J21" s="177" t="inlineStr"/>
       <c r="K21" s="177" t="inlineStr"/>
-      <c r="L21" s="177" t="inlineStr">
-        <is>
-          <t>Automated — artifacts/qa-automation/tests/smoke.spec.ts:259</t>
-        </is>
-      </c>
+      <c r="L21" s="177" t="inlineStr"/>
       <c r="M21" s="177" t="inlineStr"/>
     </row>
     <row r="22">
@@ -5116,11 +5036,7 @@
       </c>
       <c r="J22" s="177" t="inlineStr"/>
       <c r="K22" s="177" t="inlineStr"/>
-      <c r="L22" s="177" t="inlineStr">
-        <is>
-          <t>Automated — artifacts/qa-automation/tests/smoke.spec.ts:289</t>
-        </is>
-      </c>
+      <c r="L22" s="177" t="inlineStr"/>
       <c r="M22" s="177" t="inlineStr"/>
     </row>
     <row r="23">
@@ -5168,11 +5084,7 @@
       </c>
       <c r="J23" s="177" t="inlineStr"/>
       <c r="K23" s="177" t="inlineStr"/>
-      <c r="L23" s="177" t="inlineStr">
-        <is>
-          <t>Automated — artifacts/qa-automation/tests/smoke.spec.ts:295</t>
-        </is>
-      </c>
+      <c r="L23" s="177" t="inlineStr"/>
       <c r="M23" s="177" t="inlineStr"/>
     </row>
     <row r="24">
@@ -5220,11 +5132,7 @@
       </c>
       <c r="J24" s="177" t="inlineStr"/>
       <c r="K24" s="177" t="inlineStr"/>
-      <c r="L24" s="177" t="inlineStr">
-        <is>
-          <t>Automated — artifacts/qa-automation/tests/smoke.spec.ts:303</t>
-        </is>
-      </c>
+      <c r="L24" s="177" t="inlineStr"/>
       <c r="M24" s="177" t="inlineStr"/>
     </row>
   </sheetData>

--- a/docs/test-plans/qapulse-smoke-tests.xlsx
+++ b/docs/test-plans/qapulse-smoke-tests.xlsx
@@ -1844,7 +1844,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="en-US"/>
               </a:p>
@@ -2190,7 +2190,7 @@
                 </a:defRPr>
               </a:pPr>
               <a:r>
-                <a:t/>
+                <a:t>None</a:t>
               </a:r>
               <a:endParaRPr lang="en-US"/>
             </a:p>
@@ -2267,7 +2267,7 @@
                 </a:defRPr>
               </a:pPr>
               <a:r>
-                <a:t/>
+                <a:t>None</a:t>
               </a:r>
               <a:endParaRPr lang="en-US"/>
             </a:p>
@@ -2300,7 +2300,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="en-US"/>
           </a:p>
@@ -2404,7 +2404,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="en-US"/>
           </a:p>
@@ -2458,7 +2458,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="en-US"/>
         </a:p>
@@ -4073,9 +4073,17 @@
           <t>Dashboard/landing for the role loads; JWT stored; no error</t>
         </is>
       </c>
-      <c r="J2" s="177" t="inlineStr"/>
+      <c r="J2" s="177" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
       <c r="K2" s="177" t="inlineStr"/>
-      <c r="L2" s="177" t="inlineStr"/>
+      <c r="L2" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 02:47 UTC — Passed (34.9s) || Last automated run: 2026-07-19 03:22 UTC — Passed (30.2s)</t>
+        </is>
+      </c>
       <c r="M2" s="177" t="inlineStr"/>
     </row>
     <row r="3">
@@ -4122,9 +4130,17 @@
           <t>401; clear error message; no token issued</t>
         </is>
       </c>
-      <c r="J3" s="177" t="inlineStr"/>
+      <c r="J3" s="177" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
       <c r="K3" s="177" t="inlineStr"/>
-      <c r="L3" s="177" t="inlineStr"/>
+      <c r="L3" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 02:47 UTC — Passed (27.9s) || Last automated run: 2026-07-19 03:22 UTC — Passed (33.2s)</t>
+        </is>
+      </c>
       <c r="M3" s="177" t="inlineStr"/>
     </row>
     <row r="4">
@@ -4170,9 +4186,17 @@
           <t>App detects 401, clears session, redirects to /login</t>
         </is>
       </c>
-      <c r="J4" s="177" t="inlineStr"/>
+      <c r="J4" s="177" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
       <c r="K4" s="177" t="inlineStr"/>
-      <c r="L4" s="177" t="inlineStr"/>
+      <c r="L4" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 02:52 UTC — Passed (33.6s) || Last automated run: 2026-07-19 03:22 UTC — Passed (32.7s)</t>
+        </is>
+      </c>
       <c r="M4" s="177" t="inlineStr"/>
     </row>
     <row r="5">
@@ -4218,9 +4242,17 @@
           <t>Lands on /dashboard (or role home) - NOT a blank self-redirect</t>
         </is>
       </c>
-      <c r="J5" s="177" t="inlineStr"/>
+      <c r="J5" s="177" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
       <c r="K5" s="177" t="inlineStr"/>
-      <c r="L5" s="177" t="inlineStr"/>
+      <c r="L5" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 02:52 UTC — Passed (26.6s) || Last automated run: 2026-07-19 03:22 UTC — Passed (26.9s)</t>
+        </is>
+      </c>
       <c r="M5" s="177" t="inlineStr"/>
     </row>
     <row r="6">
@@ -4266,9 +4298,17 @@
           <t>Every visible nav item opens its page; no bounce to /dashboard</t>
         </is>
       </c>
-      <c r="J6" s="177" t="inlineStr"/>
+      <c r="J6" s="177" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
       <c r="K6" s="177" t="inlineStr"/>
-      <c r="L6" s="177" t="inlineStr"/>
+      <c r="L6" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 02:52 UTC — Passed (34.0s) || Last automated run: 2026-07-19 03:22 UTC — Passed (31.8s)</t>
+        </is>
+      </c>
       <c r="M6" s="177" t="inlineStr"/>
     </row>
     <row r="7">
@@ -4314,9 +4354,17 @@
           <t>Only 'Authentication' module records shown; other modules hidden</t>
         </is>
       </c>
-      <c r="J7" s="177" t="inlineStr"/>
+      <c r="J7" s="177" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
       <c r="K7" s="177" t="inlineStr"/>
-      <c r="L7" s="177" t="inlineStr"/>
+      <c r="L7" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 02:52 UTC — Passed (1.3s) || Last automated run: 2026-07-19 03:22 UTC — Passed (1.2s)</t>
+        </is>
+      </c>
       <c r="M7" s="177" t="inlineStr"/>
     </row>
     <row r="8">
@@ -4361,9 +4409,17 @@
           <t>401 Unauthorized on each (no data returned)</t>
         </is>
       </c>
-      <c r="J8" s="177" t="inlineStr"/>
+      <c r="J8" s="177" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
       <c r="K8" s="177" t="inlineStr"/>
-      <c r="L8" s="177" t="inlineStr"/>
+      <c r="L8" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 02:52 UTC — Passed (0.4s) || Last automated run: 2026-07-19 03:22 UTC — Passed (0.4s)</t>
+        </is>
+      </c>
       <c r="M8" s="177" t="inlineStr"/>
     </row>
     <row r="9">
@@ -4410,9 +4466,17 @@
           <t>Requirement created in draft; appears in list; assignee notified if set</t>
         </is>
       </c>
-      <c r="J9" s="177" t="inlineStr"/>
+      <c r="J9" s="177" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
       <c r="K9" s="177" t="inlineStr"/>
-      <c r="L9" s="177" t="inlineStr"/>
+      <c r="L9" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 02:52 UTC — Passed (0.2s) || Last automated run: 2026-07-19 03:22 UTC — Passed (0.2s)</t>
+        </is>
+      </c>
       <c r="M9" s="177" t="inlineStr"/>
     </row>
     <row r="10">
@@ -4458,9 +4522,17 @@
           <t>Status -&gt; in_review; FA reviewers on the project (module-scoped) notified</t>
         </is>
       </c>
-      <c r="J10" s="177" t="inlineStr"/>
+      <c r="J10" s="177" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
       <c r="K10" s="177" t="inlineStr"/>
-      <c r="L10" s="177" t="inlineStr"/>
+      <c r="L10" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 02:52 UTC — Passed (0.4s) || Last automated run: 2026-07-19 03:22 UTC — Passed (0.3s)</t>
+        </is>
+      </c>
       <c r="M10" s="177" t="inlineStr"/>
     </row>
     <row r="11">
@@ -4506,9 +4578,17 @@
           <t>Status -&gt; approved; author + dev_lead (module-scoped) notified</t>
         </is>
       </c>
-      <c r="J11" s="177" t="inlineStr"/>
+      <c r="J11" s="177" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
       <c r="K11" s="177" t="inlineStr"/>
-      <c r="L11" s="177" t="inlineStr"/>
+      <c r="L11" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 02:52 UTC — Passed (0.6s) || Last automated run: 2026-07-19 03:22 UTC — Passed (0.5s)</t>
+        </is>
+      </c>
       <c r="M11" s="177" t="inlineStr"/>
     </row>
     <row r="12">
@@ -4554,9 +4634,17 @@
           <t>Status -&gt; rejected; author + milestone PM notified</t>
         </is>
       </c>
-      <c r="J12" s="177" t="inlineStr"/>
+      <c r="J12" s="177" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
       <c r="K12" s="177" t="inlineStr"/>
-      <c r="L12" s="177" t="inlineStr"/>
+      <c r="L12" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 02:52 UTC — Passed (0.4s) || Last automated run: 2026-07-19 03:22 UTC — Passed (0.5s)</t>
+        </is>
+      </c>
       <c r="M12" s="177" t="inlineStr"/>
     </row>
     <row r="13">
@@ -4602,9 +4690,17 @@
           <t>devStatus=assigned; assigned dev notified</t>
         </is>
       </c>
-      <c r="J13" s="177" t="inlineStr"/>
+      <c r="J13" s="177" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
       <c r="K13" s="177" t="inlineStr"/>
-      <c r="L13" s="177" t="inlineStr"/>
+      <c r="L13" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 02:52 UTC — Passed (0.5s) || Last automated run: 2026-07-19 03:22 UTC — Passed (0.6s)</t>
+        </is>
+      </c>
       <c r="M13" s="177" t="inlineStr"/>
     </row>
     <row r="14">
@@ -4650,9 +4746,17 @@
           <t>devStatus=ready_for_qa; qa_lead (module-scoped) notified</t>
         </is>
       </c>
-      <c r="J14" s="177" t="inlineStr"/>
+      <c r="J14" s="177" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
       <c r="K14" s="177" t="inlineStr"/>
-      <c r="L14" s="177" t="inlineStr"/>
+      <c r="L14" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 02:52 UTC — Passed (1.0s) || Last automated run: 2026-07-19 03:22 UTC — Passed (0.9s)</t>
+        </is>
+      </c>
       <c r="M14" s="177" t="inlineStr"/>
     </row>
     <row r="15">
@@ -4698,9 +4802,17 @@
           <t>devStatus back to in_progress; dev + dev_lead notified with reason</t>
         </is>
       </c>
-      <c r="J15" s="177" t="inlineStr"/>
+      <c r="J15" s="177" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
       <c r="K15" s="177" t="inlineStr"/>
-      <c r="L15" s="177" t="inlineStr"/>
+      <c r="L15" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 02:52 UTC — Passed (0.8s) || Last automated run: 2026-07-19 03:22 UTC — Passed (1.1s)</t>
+        </is>
+      </c>
       <c r="M15" s="177" t="inlineStr"/>
     </row>
     <row r="16">
@@ -4746,9 +4858,17 @@
           <t>Status -&gt; rejected (back to author); FA author + FA team notified; dev handoff reset</t>
         </is>
       </c>
-      <c r="J16" s="177" t="inlineStr"/>
+      <c r="J16" s="177" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
       <c r="K16" s="177" t="inlineStr"/>
-      <c r="L16" s="177" t="inlineStr"/>
+      <c r="L16" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 02:52 UTC — Passed (0.5s) || Last automated run: 2026-07-19 03:22 UTC — Passed (0.6s)</t>
+        </is>
+      </c>
       <c r="M16" s="177" t="inlineStr"/>
     </row>
     <row r="17">
@@ -4794,9 +4914,17 @@
           <t>Defect created, routed to requirement author; requirement stays in progress</t>
         </is>
       </c>
-      <c r="J17" s="177" t="inlineStr"/>
+      <c r="J17" s="177" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
       <c r="K17" s="177" t="inlineStr"/>
-      <c r="L17" s="177" t="inlineStr"/>
+      <c r="L17" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 02:52 UTC — Passed (0.6s) || Last automated run: 2026-07-19 03:22 UTC — Passed (0.5s)</t>
+        </is>
+      </c>
       <c r="M17" s="177" t="inlineStr"/>
     </row>
     <row r="18">
@@ -4842,9 +4970,17 @@
           <t>File created; the named QA PIC is notified</t>
         </is>
       </c>
-      <c r="J18" s="177" t="inlineStr"/>
+      <c r="J18" s="177" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
       <c r="K18" s="177" t="inlineStr"/>
-      <c r="L18" s="177" t="inlineStr"/>
+      <c r="L18" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 02:52 UTC — Passed (0.3s) || Last automated run: 2026-07-19 03:22 UTC — Passed (0.3s)</t>
+        </is>
+      </c>
       <c r="M18" s="177" t="inlineStr"/>
     </row>
     <row r="19">
@@ -4891,9 +5027,17 @@
           <t>Results persist; pass rate updates; dashboard reflects change</t>
         </is>
       </c>
-      <c r="J19" s="177" t="inlineStr"/>
+      <c r="J19" s="177" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
       <c r="K19" s="177" t="inlineStr"/>
-      <c r="L19" s="177" t="inlineStr"/>
+      <c r="L19" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 02:52 UTC — Passed (0.3s) || Last automated run: 2026-07-19 03:22 UTC — Passed (0.3s)</t>
+        </is>
+      </c>
       <c r="M19" s="177" t="inlineStr"/>
     </row>
     <row r="20">
@@ -4939,9 +5083,17 @@
           <t>Exactly ONE local defect created (no twin on double-submit); linked to the TC</t>
         </is>
       </c>
-      <c r="J20" s="177" t="inlineStr"/>
+      <c r="J20" s="177" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
       <c r="K20" s="177" t="inlineStr"/>
-      <c r="L20" s="177" t="inlineStr"/>
+      <c r="L20" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 02:52 UTC — Passed (0.3s) || Last automated run: 2026-07-19 03:22 UTC — Passed (0.3s)</t>
+        </is>
+      </c>
       <c r="M20" s="177" t="inlineStr"/>
     </row>
     <row r="21">
@@ -4986,9 +5138,17 @@
           <t>Assigned dev gets a 'Defect reopened' notification</t>
         </is>
       </c>
-      <c r="J21" s="177" t="inlineStr"/>
+      <c r="J21" s="177" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
       <c r="K21" s="177" t="inlineStr"/>
-      <c r="L21" s="177" t="inlineStr"/>
+      <c r="L21" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 02:47 UTC — Not Executed (0.7s) || Last automated run: 2026-07-19 03:22 UTC — Not Executed (0.4s)</t>
+        </is>
+      </c>
       <c r="M21" s="177" t="inlineStr"/>
     </row>
     <row r="22">
@@ -5034,9 +5194,17 @@
           <t>Req -&gt; TC -&gt; execution result matrix renders; coverage rolled up</t>
         </is>
       </c>
-      <c r="J22" s="177" t="inlineStr"/>
+      <c r="J22" s="177" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
       <c r="K22" s="177" t="inlineStr"/>
-      <c r="L22" s="177" t="inlineStr"/>
+      <c r="L22" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 02:52 UTC — Passed (34.6s) || Last automated run: 2026-07-19 03:22 UTC — Passed (31.6s)</t>
+        </is>
+      </c>
       <c r="M22" s="177" t="inlineStr"/>
     </row>
     <row r="23">
@@ -5082,9 +5250,17 @@
           <t>Plan vs Actual phase bars, KPI cards, benchmark, blockers all render</t>
         </is>
       </c>
-      <c r="J23" s="177" t="inlineStr"/>
+      <c r="J23" s="177" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
       <c r="K23" s="177" t="inlineStr"/>
-      <c r="L23" s="177" t="inlineStr"/>
+      <c r="L23" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 02:52 UTC — Passed (30.9s) || Last automated run: 2026-07-19 03:22 UTC — Passed (31.3s)</t>
+        </is>
+      </c>
       <c r="M23" s="177" t="inlineStr"/>
     </row>
     <row r="24">
@@ -5130,9 +5306,17 @@
           <t>Navigates to the correct page; row is focused where supported (CR051)</t>
         </is>
       </c>
-      <c r="J24" s="177" t="inlineStr"/>
+      <c r="J24" s="177" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
       <c r="K24" s="177" t="inlineStr"/>
-      <c r="L24" s="177" t="inlineStr"/>
+      <c r="L24" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 02:52 UTC — Passed (30.8s) || Last automated run: 2026-07-19 03:22 UTC — Passed (30.9s)</t>
+        </is>
+      </c>
       <c r="M24" s="177" t="inlineStr"/>
     </row>
   </sheetData>
